--- a/InputData/dist-heat/BFoHPbF/BAU Frac of Heat Provided by Fuel.xlsx
+++ b/InputData/dist-heat/BFoHPbF/BAU Frac of Heat Provided by Fuel.xlsx
@@ -1,30 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10613"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28318"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anaxolt/Google Drive/2021/D.Development/TARGET_eps-us-3.2.1/InputData/zzz_dist-heat/BFoHPbF/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeff-nonadmin\CodeRepositories\eps-us\InputData\dist-heat\BFoHPbF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE154262-BA9F-3048-AABF-29B10FA8627D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{54263B1F-4804-432C-9849-66BD0A8B2C3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00F26569-887E-4609-9A6D-A39C013EA50C}"/>
   <bookViews>
-    <workbookView xWindow="1120" yWindow="1480" windowWidth="22180" windowHeight="14500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1125" yWindow="1470" windowWidth="22170" windowHeight="14490" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
-    <sheet name="Data" sheetId="2" r:id="rId2"/>
-    <sheet name="BFoHPbF" sheetId="3" r:id="rId3"/>
+    <sheet name="BFoHPbF" sheetId="3" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -32,60 +37,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+  <si>
+    <t>BFoHPbF BAU Fraction of Heat Provided by Fuel</t>
+  </si>
   <si>
     <t>Source:</t>
   </si>
   <si>
-    <t>International Energy Agency</t>
+    <t>None needed</t>
   </si>
   <si>
-    <t>CHP/DHC Country Scorecard: United States</t>
+    <t>Notes</t>
   </si>
   <si>
-    <t>http://www.iea.org/publications/insights/insightpublications/US_CountryScorecard_FINAL.pdf</t>
+    <t xml:space="preserve">In Mexico there are no District Heating systems and there are no plans for the future. </t>
   </si>
   <si>
-    <t>Page 37, Table 2, Sub-table 3</t>
-  </si>
-  <si>
-    <t>Note:</t>
-  </si>
-  <si>
-    <t>We use these as a stand-in for the fuel use fractions of district heating</t>
-  </si>
-  <si>
-    <t>systems (about half of which are CHP systems), because we do not</t>
-  </si>
-  <si>
-    <t>have data specifically on fuel use fractions of district heating systems.</t>
-  </si>
-  <si>
-    <t>Natural gas</t>
-  </si>
-  <si>
-    <t>Coal</t>
-  </si>
-  <si>
-    <t>Oil</t>
-  </si>
-  <si>
-    <t>Biogas/Biomass</t>
-  </si>
-  <si>
-    <t>Other</t>
-  </si>
-  <si>
-    <t>Fuel input for additional CHP capacity (GWh)</t>
-  </si>
-  <si>
-    <t>We don't have fuel fractions used by the total installed base, so we use</t>
-  </si>
-  <si>
-    <t>Sum of Years Above</t>
-  </si>
-  <si>
-    <t>Fraction by Fuel</t>
+    <t>Fraction of Heat Provided by Fuel (dimensionless)</t>
   </si>
   <si>
     <t>electricity</t>
@@ -106,15 +75,6 @@
     <t>heat</t>
   </si>
   <si>
-    <t>Reallocating "Other" into modeled fuel categories</t>
-  </si>
-  <si>
-    <t>the fuel fractions from the available years' newly installed capacities.</t>
-  </si>
-  <si>
-    <t>BFoHPbF BAU Fraction of Heat Provided by Fuel</t>
-  </si>
-  <si>
     <t>crude oil</t>
   </si>
   <si>
@@ -126,45 +86,12 @@
   <si>
     <t>hydrogen</t>
   </si>
-  <si>
-    <t>Fuel use by fuel (fractions) are provided for CHP systems.</t>
-  </si>
-  <si>
-    <t>Fraction of Heat Provided by Fuel (dimensionless)</t>
-  </si>
-  <si>
-    <t>Note on Heat Pumps</t>
-  </si>
-  <si>
-    <t>The "electricity" fuel type represents heat pumps.</t>
-  </si>
-  <si>
-    <t>This can be changed by altering dist-heat/EoCtUH.</t>
-  </si>
-  <si>
-    <t>SENER</t>
-  </si>
-  <si>
-    <t>National Energy Balance (BNE)</t>
-  </si>
-  <si>
-    <t>https://www.gob.mx/cms/uploads/attachment/file/288692/Balance_Nacional_de_Energ_a_2016__2_.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">For Mexico this heat fraction only applies for oil and gas. </t>
-  </si>
-  <si>
-    <t>US Source:</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.000"/>
-  </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -188,27 +115,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF3333FF"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.249977111117893"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -227,32 +140,22 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -269,9 +172,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -309,9 +212,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -344,26 +247,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -396,26 +282,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -589,538 +458,238 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B31"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:B18"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="58.1640625" customWidth="1"/>
+    <col min="2" max="2" width="58.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>36</v>
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B4" s="2">
-        <v>2016</v>
-      </c>
+    <row r="4" spans="1:2">
+      <c r="B4" s="2"/>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B5" t="s">
-        <v>37</v>
-      </c>
+    <row r="6" spans="1:2">
+      <c r="B6" s="4"/>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B6" s="13" t="s">
-        <v>38</v>
+    <row r="9" spans="1:2">
+      <c r="A9" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A9" s="1" t="s">
-        <v>5</v>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A14" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B14" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B15" s="2">
-        <v>2014</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B16" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B17" s="11" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B18" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A20" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A29" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>35</v>
-      </c>
+    <row r="18" spans="1:1">
+      <c r="A18" s="1"/>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="B17" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId2"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="16.5" customWidth="1"/>
-    <col min="2" max="2" width="19.5" customWidth="1"/>
-    <col min="3" max="3" width="17.5" customWidth="1"/>
-    <col min="4" max="4" width="12.5" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B2">
-        <v>2000</v>
-      </c>
-      <c r="C2">
-        <v>2006</v>
-      </c>
-      <c r="D2">
-        <v>2008</v>
-      </c>
-      <c r="E2">
-        <v>2009</v>
-      </c>
-      <c r="F2">
-        <v>2020</v>
-      </c>
-      <c r="G2">
-        <v>2022</v>
-      </c>
-      <c r="H2">
-        <v>2012</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3">
-        <v>55622.2</v>
-      </c>
-      <c r="C3">
-        <v>7957.9</v>
-      </c>
-      <c r="D3">
-        <v>5249.4</v>
-      </c>
-      <c r="E3">
-        <v>5271</v>
-      </c>
-      <c r="F3">
-        <v>14497.7</v>
-      </c>
-      <c r="G3">
-        <v>5215.6000000000004</v>
-      </c>
-      <c r="H3">
-        <v>8544</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4">
-        <v>8003.3</v>
-      </c>
-      <c r="C4">
-        <v>876</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>3551.7</v>
-      </c>
-      <c r="F4">
-        <v>1513.1</v>
-      </c>
-      <c r="G4">
-        <v>995.4</v>
-      </c>
-      <c r="H4">
-        <v>12343.4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5">
-        <v>4050.7</v>
-      </c>
-      <c r="C5">
-        <v>456.6</v>
-      </c>
-      <c r="D5">
-        <v>18.5</v>
-      </c>
-      <c r="E5">
-        <v>568.20000000000005</v>
-      </c>
-      <c r="F5">
-        <v>115.9</v>
-      </c>
-      <c r="G5">
-        <v>23</v>
-      </c>
-      <c r="H5">
-        <v>199.7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6">
-        <v>1090.2</v>
-      </c>
-      <c r="C6">
-        <v>2533.9</v>
-      </c>
-      <c r="D6">
-        <v>859.4</v>
-      </c>
-      <c r="E6">
-        <v>10628.4</v>
-      </c>
-      <c r="F6">
-        <v>1133.5</v>
-      </c>
-      <c r="G6">
-        <v>4829.3999999999996</v>
-      </c>
-      <c r="H6">
-        <v>4055.7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7">
-        <v>7030.9</v>
-      </c>
-      <c r="C7">
-        <v>4116.6000000000004</v>
-      </c>
-      <c r="D7">
-        <v>6967.4</v>
-      </c>
-      <c r="E7">
-        <v>4280.5</v>
-      </c>
-      <c r="F7">
-        <v>468.1</v>
-      </c>
-      <c r="G7">
-        <v>10068.299999999999</v>
-      </c>
-      <c r="H7">
-        <v>2641.4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B9" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="7">
-        <f>SUM(B3:H3)</f>
-        <v>102357.8</v>
-      </c>
-      <c r="C10" s="8">
-        <f>B10/SUM(B$10:B$14)</f>
-        <v>0.52282852429039151</v>
-      </c>
-      <c r="D10" s="8">
-        <f>C10+C$14*(C10/SUM(C$10:C$13))</f>
-        <v>0.63892242256425869</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" s="7">
-        <f t="shared" ref="B11:B14" si="0">SUM(B4:H4)</f>
-        <v>27282.9</v>
-      </c>
-      <c r="C11" s="8">
-        <f t="shared" ref="C11:C14" si="1">B11/SUM(B$10:B$14)</f>
-        <v>0.13935702355230695</v>
-      </c>
-      <c r="D11" s="8">
-        <f t="shared" ref="D11:D13" si="2">C11+C$14*(C11/SUM(C$10:C$13))</f>
-        <v>0.17030120384160674</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" s="7">
-        <f t="shared" si="0"/>
-        <v>5432.5999999999995</v>
-      </c>
-      <c r="C12" s="8">
-        <f t="shared" si="1"/>
-        <v>2.7748918412275184E-2</v>
-      </c>
-      <c r="D12" s="8">
-        <f t="shared" si="2"/>
-        <v>3.3910556428748871E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>12</v>
-      </c>
-      <c r="B13" s="7">
-        <f t="shared" si="0"/>
-        <v>25130.5</v>
-      </c>
-      <c r="C13" s="8">
-        <f t="shared" si="1"/>
-        <v>0.12836288225889658</v>
-      </c>
-      <c r="D13" s="8">
-        <f t="shared" si="2"/>
-        <v>0.15686581716538556</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" s="7">
-        <f t="shared" si="0"/>
-        <v>35573.200000000004</v>
-      </c>
-      <c r="C14" s="8">
-        <f t="shared" si="1"/>
-        <v>0.18170265148612963</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AK11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:BE11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="24.1640625" customWidth="1"/>
-    <col min="2" max="2" width="9.5" customWidth="1"/>
+    <col min="1" max="1" width="24.140625" customWidth="1"/>
+    <col min="2" max="2" width="9.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" ht="32" x14ac:dyDescent="0.2">
-      <c r="A1" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="B1" s="9">
+    <row r="1" spans="1:57" ht="30">
+      <c r="A1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="3">
         <v>2015</v>
       </c>
       <c r="C1">
         <v>2016</v>
       </c>
-      <c r="D1" s="9">
+      <c r="D1" s="3">
         <v>2017</v>
       </c>
       <c r="E1">
         <v>2018</v>
       </c>
-      <c r="F1" s="9">
+      <c r="F1" s="3">
         <v>2019</v>
       </c>
       <c r="G1">
         <v>2020</v>
       </c>
-      <c r="H1" s="9">
+      <c r="H1" s="3">
         <v>2021</v>
       </c>
       <c r="I1">
         <v>2022</v>
       </c>
-      <c r="J1" s="9">
+      <c r="J1" s="3">
         <v>2023</v>
       </c>
       <c r="K1">
         <v>2024</v>
       </c>
-      <c r="L1" s="9">
+      <c r="L1" s="3">
         <v>2025</v>
       </c>
       <c r="M1">
         <v>2026</v>
       </c>
-      <c r="N1" s="9">
+      <c r="N1" s="3">
         <v>2027</v>
       </c>
       <c r="O1">
         <v>2028</v>
       </c>
-      <c r="P1" s="9">
+      <c r="P1" s="3">
         <v>2029</v>
       </c>
       <c r="Q1">
         <v>2030</v>
       </c>
-      <c r="R1" s="9">
+      <c r="R1" s="3">
         <v>2031</v>
       </c>
       <c r="S1">
         <v>2032</v>
       </c>
-      <c r="T1" s="9">
+      <c r="T1" s="3">
         <v>2033</v>
       </c>
       <c r="U1">
         <v>2034</v>
       </c>
-      <c r="V1" s="9">
+      <c r="V1" s="3">
         <v>2035</v>
       </c>
       <c r="W1">
         <v>2036</v>
       </c>
-      <c r="X1" s="9">
+      <c r="X1" s="3">
         <v>2037</v>
       </c>
       <c r="Y1">
         <v>2038</v>
       </c>
-      <c r="Z1" s="9">
+      <c r="Z1" s="3">
         <v>2039</v>
       </c>
       <c r="AA1">
         <v>2040</v>
       </c>
-      <c r="AB1" s="9">
+      <c r="AB1" s="3">
         <v>2041</v>
       </c>
       <c r="AC1">
         <v>2042</v>
       </c>
-      <c r="AD1" s="9">
+      <c r="AD1" s="3">
         <v>2043</v>
       </c>
       <c r="AE1">
         <v>2044</v>
       </c>
-      <c r="AF1" s="9">
+      <c r="AF1" s="3">
         <v>2045</v>
       </c>
       <c r="AG1">
         <v>2046</v>
       </c>
-      <c r="AH1" s="9">
+      <c r="AH1" s="3">
         <v>2047</v>
       </c>
       <c r="AI1">
         <v>2048</v>
       </c>
-      <c r="AJ1" s="9">
+      <c r="AJ1" s="3">
         <v>2049</v>
       </c>
       <c r="AK1">
         <v>2050</v>
       </c>
+      <c r="AL1" s="3">
+        <v>2051</v>
+      </c>
+      <c r="AM1">
+        <v>2052</v>
+      </c>
+      <c r="AN1" s="3">
+        <v>2053</v>
+      </c>
+      <c r="AO1">
+        <v>2054</v>
+      </c>
+      <c r="AP1" s="3">
+        <v>2055</v>
+      </c>
+      <c r="AQ1">
+        <v>2056</v>
+      </c>
+      <c r="AR1" s="3">
+        <v>2057</v>
+      </c>
+      <c r="AS1">
+        <v>2058</v>
+      </c>
+      <c r="AT1" s="3">
+        <v>2059</v>
+      </c>
+      <c r="AU1">
+        <v>2060</v>
+      </c>
+      <c r="AV1" s="3">
+        <v>2061</v>
+      </c>
+      <c r="AW1">
+        <v>2062</v>
+      </c>
+      <c r="AX1" s="3">
+        <v>2063</v>
+      </c>
+      <c r="AY1" s="3">
+        <v>2064</v>
+      </c>
+      <c r="AZ1">
+        <v>2065</v>
+      </c>
+      <c r="BA1" s="3">
+        <v>2066</v>
+      </c>
+      <c r="BB1">
+        <v>2067</v>
+      </c>
+      <c r="BC1" s="3">
+        <v>2068</v>
+      </c>
+      <c r="BD1">
+        <v>2069</v>
+      </c>
+      <c r="BE1" s="3">
+        <v>2070</v>
+      </c>
     </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:57">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1230,12 +799,72 @@
       <c r="AK2">
         <v>0</v>
       </c>
+      <c r="AL2">
+        <v>0</v>
+      </c>
+      <c r="AM2">
+        <v>0</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>0</v>
+      </c>
+      <c r="AP2">
+        <v>0</v>
+      </c>
+      <c r="AQ2">
+        <v>0</v>
+      </c>
+      <c r="AR2">
+        <v>0</v>
+      </c>
+      <c r="AS2">
+        <v>0</v>
+      </c>
+      <c r="AT2">
+        <v>0</v>
+      </c>
+      <c r="AU2">
+        <v>0</v>
+      </c>
+      <c r="AV2">
+        <v>0</v>
+      </c>
+      <c r="AW2">
+        <v>0</v>
+      </c>
+      <c r="AX2">
+        <v>0</v>
+      </c>
+      <c r="AY2">
+        <v>0</v>
+      </c>
+      <c r="AZ2">
+        <v>0</v>
+      </c>
+      <c r="BA2">
+        <v>0</v>
+      </c>
+      <c r="BB2">
+        <v>0</v>
+      </c>
+      <c r="BC2">
+        <v>0</v>
+      </c>
+      <c r="BD2">
+        <v>0</v>
+      </c>
+      <c r="BE2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:57">
       <c r="A3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" s="10">
+        <v>7</v>
+      </c>
+      <c r="B3">
         <v>0</v>
       </c>
       <c r="C3">
@@ -1343,125 +972,245 @@
       <c r="AK3">
         <v>0</v>
       </c>
+      <c r="AL3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <v>0</v>
+      </c>
+      <c r="AN3">
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <v>0</v>
+      </c>
+      <c r="AQ3">
+        <v>0</v>
+      </c>
+      <c r="AR3">
+        <v>0</v>
+      </c>
+      <c r="AS3">
+        <v>0</v>
+      </c>
+      <c r="AT3">
+        <v>0</v>
+      </c>
+      <c r="AU3">
+        <v>0</v>
+      </c>
+      <c r="AV3">
+        <v>0</v>
+      </c>
+      <c r="AW3">
+        <v>0</v>
+      </c>
+      <c r="AX3">
+        <v>0</v>
+      </c>
+      <c r="AY3">
+        <v>0</v>
+      </c>
+      <c r="AZ3">
+        <v>0</v>
+      </c>
+      <c r="BA3">
+        <v>0</v>
+      </c>
+      <c r="BB3">
+        <v>0</v>
+      </c>
+      <c r="BC3">
+        <v>0</v>
+      </c>
+      <c r="BD3">
+        <v>0</v>
+      </c>
+      <c r="BE3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:57">
       <c r="A4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" s="10">
-        <v>0.88660000000000005</v>
+        <v>8</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>0.88660000000000005</v>
+        <v>0</v>
       </c>
       <c r="D4">
-        <v>0.88660000000000005</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0.88660000000000005</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>0.88660000000000005</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>0.88660000000000005</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>0.88660000000000005</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>0.88660000000000005</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>0.88660000000000005</v>
+        <v>0</v>
       </c>
       <c r="K4">
-        <v>0.88660000000000005</v>
+        <v>0</v>
       </c>
       <c r="L4">
-        <v>0.88660000000000005</v>
+        <v>0</v>
       </c>
       <c r="M4">
-        <v>0.88660000000000005</v>
+        <v>0</v>
       </c>
       <c r="N4">
-        <v>0.88660000000000005</v>
+        <v>0</v>
       </c>
       <c r="O4">
-        <v>0.88660000000000005</v>
+        <v>0</v>
       </c>
       <c r="P4">
-        <v>0.88660000000000005</v>
+        <v>0</v>
       </c>
       <c r="Q4">
-        <v>0.88660000000000005</v>
+        <v>0</v>
       </c>
       <c r="R4">
-        <v>0.88660000000000005</v>
+        <v>0</v>
       </c>
       <c r="S4">
-        <v>0.88660000000000005</v>
+        <v>0</v>
       </c>
       <c r="T4">
-        <v>0.88660000000000005</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>0.88660000000000005</v>
+        <v>0</v>
       </c>
       <c r="V4">
-        <v>0.88660000000000005</v>
+        <v>0</v>
       </c>
       <c r="W4">
-        <v>0.88660000000000005</v>
+        <v>0</v>
       </c>
       <c r="X4">
-        <v>0.88660000000000005</v>
+        <v>0</v>
       </c>
       <c r="Y4">
-        <v>0.88660000000000005</v>
+        <v>0</v>
       </c>
       <c r="Z4">
-        <v>0.88660000000000005</v>
+        <v>0</v>
       </c>
       <c r="AA4">
-        <v>0.88660000000000005</v>
+        <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.88660000000000005</v>
+        <v>0</v>
       </c>
       <c r="AC4">
-        <v>0.88660000000000005</v>
+        <v>0</v>
       </c>
       <c r="AD4">
-        <v>0.88660000000000005</v>
+        <v>0</v>
       </c>
       <c r="AE4">
-        <v>0.88660000000000005</v>
+        <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.88660000000000005</v>
+        <v>0</v>
       </c>
       <c r="AG4">
-        <v>0.88660000000000005</v>
+        <v>0</v>
       </c>
       <c r="AH4">
-        <v>0.88660000000000005</v>
+        <v>0</v>
       </c>
       <c r="AI4">
-        <v>0.88660000000000005</v>
+        <v>0</v>
       </c>
       <c r="AJ4">
-        <v>0.88660000000000005</v>
+        <v>0</v>
       </c>
       <c r="AK4">
-        <v>0.88660000000000005</v>
+        <v>0</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+      <c r="AN4">
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <v>0</v>
+      </c>
+      <c r="AQ4">
+        <v>0</v>
+      </c>
+      <c r="AR4">
+        <v>0</v>
+      </c>
+      <c r="AS4">
+        <v>0</v>
+      </c>
+      <c r="AT4">
+        <v>0</v>
+      </c>
+      <c r="AU4">
+        <v>0</v>
+      </c>
+      <c r="AV4">
+        <v>0</v>
+      </c>
+      <c r="AW4">
+        <v>0</v>
+      </c>
+      <c r="AX4">
+        <v>0</v>
+      </c>
+      <c r="AY4">
+        <v>0</v>
+      </c>
+      <c r="AZ4">
+        <v>0</v>
+      </c>
+      <c r="BA4">
+        <v>0</v>
+      </c>
+      <c r="BB4">
+        <v>0</v>
+      </c>
+      <c r="BC4">
+        <v>0</v>
+      </c>
+      <c r="BD4">
+        <v>0</v>
+      </c>
+      <c r="BE4">
+        <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:57">
       <c r="A5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" s="10">
+        <v>9</v>
+      </c>
+      <c r="B5">
         <v>0</v>
       </c>
       <c r="C5">
@@ -1569,123 +1318,243 @@
       <c r="AK5">
         <v>0</v>
       </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+      <c r="AN5">
+        <v>0</v>
+      </c>
+      <c r="AO5">
+        <v>0</v>
+      </c>
+      <c r="AP5">
+        <v>0</v>
+      </c>
+      <c r="AQ5">
+        <v>0</v>
+      </c>
+      <c r="AR5">
+        <v>0</v>
+      </c>
+      <c r="AS5">
+        <v>0</v>
+      </c>
+      <c r="AT5">
+        <v>0</v>
+      </c>
+      <c r="AU5">
+        <v>0</v>
+      </c>
+      <c r="AV5">
+        <v>0</v>
+      </c>
+      <c r="AW5">
+        <v>0</v>
+      </c>
+      <c r="AX5">
+        <v>0</v>
+      </c>
+      <c r="AY5">
+        <v>0</v>
+      </c>
+      <c r="AZ5">
+        <v>0</v>
+      </c>
+      <c r="BA5">
+        <v>0</v>
+      </c>
+      <c r="BB5">
+        <v>0</v>
+      </c>
+      <c r="BC5">
+        <v>0</v>
+      </c>
+      <c r="BD5">
+        <v>0</v>
+      </c>
+      <c r="BE5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:57">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="B6">
-        <v>0.11339999999999995</v>
+        <v>0</v>
       </c>
       <c r="C6">
-        <v>0.11339999999999995</v>
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>0.11339999999999995</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>0.11339999999999995</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>0.11339999999999995</v>
+        <v>0</v>
       </c>
       <c r="G6">
-        <v>0.11339999999999995</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>0.11339999999999995</v>
+        <v>0</v>
       </c>
       <c r="I6">
-        <v>0.11339999999999995</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>0.11339999999999995</v>
+        <v>0</v>
       </c>
       <c r="K6">
-        <v>0.11339999999999995</v>
+        <v>0</v>
       </c>
       <c r="L6">
-        <v>0.11339999999999995</v>
+        <v>0</v>
       </c>
       <c r="M6">
-        <v>0.11339999999999995</v>
+        <v>0</v>
       </c>
       <c r="N6">
-        <v>0.11339999999999995</v>
+        <v>0</v>
       </c>
       <c r="O6">
-        <v>0.11339999999999995</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>0.11339999999999995</v>
+        <v>0</v>
       </c>
       <c r="Q6">
-        <v>0.11339999999999995</v>
+        <v>0</v>
       </c>
       <c r="R6">
-        <v>0.11339999999999995</v>
+        <v>0</v>
       </c>
       <c r="S6">
-        <v>0.11339999999999995</v>
+        <v>0</v>
       </c>
       <c r="T6">
-        <v>0.11339999999999995</v>
+        <v>0</v>
       </c>
       <c r="U6">
-        <v>0.11339999999999995</v>
+        <v>0</v>
       </c>
       <c r="V6">
-        <v>0.11339999999999995</v>
+        <v>0</v>
       </c>
       <c r="W6">
-        <v>0.11339999999999995</v>
+        <v>0</v>
       </c>
       <c r="X6">
-        <v>0.11339999999999995</v>
+        <v>0</v>
       </c>
       <c r="Y6">
-        <v>0.11339999999999995</v>
+        <v>0</v>
       </c>
       <c r="Z6">
-        <v>0.11339999999999995</v>
+        <v>0</v>
       </c>
       <c r="AA6">
-        <v>0.11339999999999995</v>
+        <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.11339999999999995</v>
+        <v>0</v>
       </c>
       <c r="AC6">
-        <v>0.11339999999999995</v>
+        <v>0</v>
       </c>
       <c r="AD6">
-        <v>0.11339999999999995</v>
+        <v>0</v>
       </c>
       <c r="AE6">
-        <v>0.11339999999999995</v>
+        <v>0</v>
       </c>
       <c r="AF6">
-        <v>0.11339999999999995</v>
+        <v>0</v>
       </c>
       <c r="AG6">
-        <v>0.11339999999999995</v>
+        <v>0</v>
       </c>
       <c r="AH6">
-        <v>0.11339999999999995</v>
+        <v>0</v>
       </c>
       <c r="AI6">
-        <v>0.11339999999999995</v>
+        <v>0</v>
       </c>
       <c r="AJ6">
-        <v>0.11339999999999995</v>
+        <v>0</v>
       </c>
       <c r="AK6">
-        <v>0.11339999999999995</v>
+        <v>0</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+      <c r="AN6">
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <v>0</v>
+      </c>
+      <c r="AQ6">
+        <v>0</v>
+      </c>
+      <c r="AR6">
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <v>0</v>
+      </c>
+      <c r="AT6">
+        <v>0</v>
+      </c>
+      <c r="AU6">
+        <v>0</v>
+      </c>
+      <c r="AV6">
+        <v>0</v>
+      </c>
+      <c r="AW6">
+        <v>0</v>
+      </c>
+      <c r="AX6">
+        <v>0</v>
+      </c>
+      <c r="AY6">
+        <v>0</v>
+      </c>
+      <c r="AZ6">
+        <v>0</v>
+      </c>
+      <c r="BA6">
+        <v>0</v>
+      </c>
+      <c r="BB6">
+        <v>0</v>
+      </c>
+      <c r="BC6">
+        <v>0</v>
+      </c>
+      <c r="BD6">
+        <v>0</v>
+      </c>
+      <c r="BE6">
+        <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:57">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1795,10 +1664,70 @@
       <c r="AK7">
         <v>0</v>
       </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+      <c r="AN7">
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <v>0</v>
+      </c>
+      <c r="AQ7">
+        <v>0</v>
+      </c>
+      <c r="AR7">
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <v>0</v>
+      </c>
+      <c r="AV7">
+        <v>0</v>
+      </c>
+      <c r="AW7">
+        <v>0</v>
+      </c>
+      <c r="AX7">
+        <v>0</v>
+      </c>
+      <c r="AY7">
+        <v>0</v>
+      </c>
+      <c r="AZ7">
+        <v>0</v>
+      </c>
+      <c r="BA7">
+        <v>0</v>
+      </c>
+      <c r="BB7">
+        <v>0</v>
+      </c>
+      <c r="BC7">
+        <v>0</v>
+      </c>
+      <c r="BD7">
+        <v>0</v>
+      </c>
+      <c r="BE7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:57">
       <c r="A8" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1908,10 +1837,70 @@
       <c r="AK8">
         <v>0</v>
       </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>0</v>
+      </c>
+      <c r="AN8">
+        <v>0</v>
+      </c>
+      <c r="AO8">
+        <v>0</v>
+      </c>
+      <c r="AP8">
+        <v>0</v>
+      </c>
+      <c r="AQ8">
+        <v>0</v>
+      </c>
+      <c r="AR8">
+        <v>0</v>
+      </c>
+      <c r="AS8">
+        <v>0</v>
+      </c>
+      <c r="AT8">
+        <v>0</v>
+      </c>
+      <c r="AU8">
+        <v>0</v>
+      </c>
+      <c r="AV8">
+        <v>0</v>
+      </c>
+      <c r="AW8">
+        <v>0</v>
+      </c>
+      <c r="AX8">
+        <v>0</v>
+      </c>
+      <c r="AY8">
+        <v>0</v>
+      </c>
+      <c r="AZ8">
+        <v>0</v>
+      </c>
+      <c r="BA8">
+        <v>0</v>
+      </c>
+      <c r="BB8">
+        <v>0</v>
+      </c>
+      <c r="BC8">
+        <v>0</v>
+      </c>
+      <c r="BD8">
+        <v>0</v>
+      </c>
+      <c r="BE8">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:57">
       <c r="A9" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -2021,10 +2010,70 @@
       <c r="AK9">
         <v>0</v>
       </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>0</v>
+      </c>
+      <c r="AN9">
+        <v>0</v>
+      </c>
+      <c r="AO9">
+        <v>0</v>
+      </c>
+      <c r="AP9">
+        <v>0</v>
+      </c>
+      <c r="AQ9">
+        <v>0</v>
+      </c>
+      <c r="AR9">
+        <v>0</v>
+      </c>
+      <c r="AS9">
+        <v>0</v>
+      </c>
+      <c r="AT9">
+        <v>0</v>
+      </c>
+      <c r="AU9">
+        <v>0</v>
+      </c>
+      <c r="AV9">
+        <v>0</v>
+      </c>
+      <c r="AW9">
+        <v>0</v>
+      </c>
+      <c r="AX9">
+        <v>0</v>
+      </c>
+      <c r="AY9">
+        <v>0</v>
+      </c>
+      <c r="AZ9">
+        <v>0</v>
+      </c>
+      <c r="BA9">
+        <v>0</v>
+      </c>
+      <c r="BB9">
+        <v>0</v>
+      </c>
+      <c r="BC9">
+        <v>0</v>
+      </c>
+      <c r="BD9">
+        <v>0</v>
+      </c>
+      <c r="BE9">
+        <v>0</v>
+      </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:57">
       <c r="A10" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -2134,10 +2183,70 @@
       <c r="AK10">
         <v>0</v>
       </c>
+      <c r="AL10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <v>0</v>
+      </c>
+      <c r="AN10">
+        <v>0</v>
+      </c>
+      <c r="AO10">
+        <v>0</v>
+      </c>
+      <c r="AP10">
+        <v>0</v>
+      </c>
+      <c r="AQ10">
+        <v>0</v>
+      </c>
+      <c r="AR10">
+        <v>0</v>
+      </c>
+      <c r="AS10">
+        <v>0</v>
+      </c>
+      <c r="AT10">
+        <v>0</v>
+      </c>
+      <c r="AU10">
+        <v>0</v>
+      </c>
+      <c r="AV10">
+        <v>0</v>
+      </c>
+      <c r="AW10">
+        <v>0</v>
+      </c>
+      <c r="AX10">
+        <v>0</v>
+      </c>
+      <c r="AY10">
+        <v>0</v>
+      </c>
+      <c r="AZ10">
+        <v>0</v>
+      </c>
+      <c r="BA10">
+        <v>0</v>
+      </c>
+      <c r="BB10">
+        <v>0</v>
+      </c>
+      <c r="BC10">
+        <v>0</v>
+      </c>
+      <c r="BD10">
+        <v>0</v>
+      </c>
+      <c r="BE10">
+        <v>0</v>
+      </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:57">
       <c r="A11" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -2245,6 +2354,66 @@
         <v>0</v>
       </c>
       <c r="AK11">
+        <v>0</v>
+      </c>
+      <c r="AL11">
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <v>0</v>
+      </c>
+      <c r="AN11">
+        <v>0</v>
+      </c>
+      <c r="AO11">
+        <v>0</v>
+      </c>
+      <c r="AP11">
+        <v>0</v>
+      </c>
+      <c r="AQ11">
+        <v>0</v>
+      </c>
+      <c r="AR11">
+        <v>0</v>
+      </c>
+      <c r="AS11">
+        <v>0</v>
+      </c>
+      <c r="AT11">
+        <v>0</v>
+      </c>
+      <c r="AU11">
+        <v>0</v>
+      </c>
+      <c r="AV11">
+        <v>0</v>
+      </c>
+      <c r="AW11">
+        <v>0</v>
+      </c>
+      <c r="AX11">
+        <v>0</v>
+      </c>
+      <c r="AY11">
+        <v>0</v>
+      </c>
+      <c r="AZ11">
+        <v>0</v>
+      </c>
+      <c r="BA11">
+        <v>0</v>
+      </c>
+      <c r="BB11">
+        <v>0</v>
+      </c>
+      <c r="BC11">
+        <v>0</v>
+      </c>
+      <c r="BD11">
+        <v>0</v>
+      </c>
+      <c r="BE11">
         <v>0</v>
       </c>
     </row>
@@ -2252,4 +2421,175 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009A9DAB439B36DB4795F39C4E722C7BC4" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="44674c89fa9bc5e97a878a6680c46188">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="79748b23-d81a-423e-9112-21109dc864e6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="447839a363ea5a12024b5bf1ab53ed90" ns2:_="">
+    <xsd:import namespace="79748b23-d81a-423e-9112-21109dc864e6"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="79748b23-d81a-423e-9112-21109dc864e6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{608772D0-2B74-4726-81F7-2CCD42B28368}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0EF24B69-CDD5-4E6C-9CEC-AC7AD8D22552}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83065D64-D4D1-499B-A0F4-4BAF6B5DCE6D}"/>
 </file>